--- a/data/bigdataball/07-30-2026-wnba-season-team-feed.xlsx
+++ b/data/bigdataball/07-30-2026-wnba-season-team-feed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\Apps\26-wnba-team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51D5F6CA-F3A9-4A5D-AAD9-09FF161D19DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B79B9316-AEC0-4AB1-AFB7-16A6B22D8D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6268" uniqueCount="1241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6268" uniqueCount="1240">
   <si>
     <t>DATASET</t>
   </si>
@@ -3835,16 +3835,13 @@
     <t>07/30/2026</t>
   </si>
   <si>
-    <t>-748</t>
-  </si>
-  <si>
     <t>185o -115</t>
   </si>
   <si>
-    <t>+504</t>
-  </si>
-  <si>
     <t>176o -110</t>
+  </si>
+  <si>
+    <t>+500</t>
   </si>
 </sst>
 </file>
@@ -62895,7 +62892,7 @@
         <v>329</v>
       </c>
       <c r="AS422" s="69" t="s">
-        <v>1237</v>
+        <v>130</v>
       </c>
     </row>
     <row r="423" spans="1:45" x14ac:dyDescent="0.25">
@@ -63020,7 +63017,7 @@
         <v>184.5</v>
       </c>
       <c r="AO423" s="62" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="AP423" s="33">
         <v>12.5</v>
@@ -63157,7 +63154,7 @@
         <v>171.5</v>
       </c>
       <c r="AO424" s="68" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="AP424" s="35">
         <v>5.5</v>
@@ -63169,7 +63166,7 @@
         <v>833</v>
       </c>
       <c r="AS424" s="70" t="s">
-        <v>1229</v>
+        <v>939</v>
       </c>
     </row>
     <row r="425" spans="1:45" x14ac:dyDescent="0.25">
@@ -63306,7 +63303,7 @@
         <v>535</v>
       </c>
       <c r="AS425" s="70" t="s">
-        <v>1227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="426" spans="1:45" x14ac:dyDescent="0.25">
@@ -63443,7 +63440,7 @@
         <v>395</v>
       </c>
       <c r="AS426" s="69" t="s">
-        <v>364</v>
+        <v>478</v>
       </c>
     </row>
     <row r="427" spans="1:45" x14ac:dyDescent="0.25">
@@ -63580,7 +63577,7 @@
         <v>398</v>
       </c>
       <c r="AS427" s="69" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
   </sheetData>
